--- a/VaultViewer/VaultViewer/DataAccessLayer/Data/EmployeeData.xlsx
+++ b/VaultViewer/VaultViewer/DataAccessLayer/Data/EmployeeData.xlsx
@@ -116,156 +116,6 @@
   </x:si>
   <x:si>
     <x:t>0987654321</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>John Doe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Private Rd 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Leuven</x:t>
-  </x:si>
-  <x:si>
-    <x:t>john.doe@example.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0478123456</x:t>
-  </x:si>
-  <x:si>
-    <x:t>False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Blue Horizon Ltd.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ocean Drive 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Brugge</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Linda Vermeer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>info@bluehorizon.be</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+32 50 123 456</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Maxime De Clercq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kapellestraat 98</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bus 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Antwerpen</x:t>
-  </x:si>
-  <x:si>
-    <x:t>maxime.dc@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+32 3 456 789</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EcoGreen BV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Groenstraat 21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hasselt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sofie Janssen</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE9876543210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>contact@ecogreen.be</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+32 11 987 654</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Julia Peeters</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Parklaan 45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>julia.peeters@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+32 9 222 333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nova Technologies</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Industrieweg 7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unit B</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3600</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Genk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Koen Desmet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE1122334455</x:t>
-  </x:si>
-  <x:si>
-    <x:t>info@novatech.be</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+32 89 555 888</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -616,7 +466,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:M9"/>
+  <x:dimension ref="A1:M3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:13">
@@ -740,252 +590,6 @@
       </x:c>
       <x:c r="M3" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:13">
-      <x:c r="A4" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:13">
-      <x:c r="A5" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:13">
-      <x:c r="A6" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="M6" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:13">
-      <x:c r="A7" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="M7" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:13">
-      <x:c r="A8" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:13">
-      <x:c r="A9" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>41</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
